--- a/data/xlsx/regon.xlsx
+++ b/data/xlsx/regon.xlsx
@@ -185,7 +185,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>biuro@astra-finance.pl</t>
+          <t>biuro@onet.pl</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -272,7 +272,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>office.baltic-med-supply@biuro.pl</t>
+          <t>office.baltic-med-supply@interia.pl</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -359,7 +359,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>kontakt.helios-markets@kancelaria.pl</t>
+          <t>kontakt.helios-markets@brak-domeny</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>biuro.lumen-advisory@ubezpieczenia.pl</t>
+          <t>biuro.lumen-advisory@proton.me</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>sekretariat.nova-data@nova-data.pl</t>
+          <t>sekretariat.nova-data@outlook.com</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>firma.optima-trade@firma.local</t>
+          <t>firma.optima-trade@yahoo.com</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>kontakt@finanse.pl</t>
+          <t>kontakt@icloud.com</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>biuro@biuro.pl</t>
+          <t>biuro@localhost</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>office.silesia-invest@silesia-invest.pl</t>
+          <t>office.silesia-invest@wp.pl</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@ubezpieczenia.pl</t>
+          <t>kontakt.vistula-fintech@onet.pl</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>biuro.astra-finance@broker.local</t>
+          <t>biuro.astra-finance@interia.pl</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sekretariat.baltic-med-supply@firma.local</t>
+          <t>sekretariat.baltic-med-supply@o2.pl</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>firma.helios-markets@helios-markets.pl</t>
+          <t>firma.helios-markets@brak-domeny</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>kontakt@biuro.pl</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>biuro@kancelaria.pl</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>office.optima-trade@ubezpieczenia.pl</t>
+          <t>office.optima-trade@icloud.com</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@polaris-capital.pl</t>
+          <t>kontakt.polaris-capital@gmail.com</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>biuro.quantum-services@firma.local</t>
+          <t>biuro.quantum-services@localhost</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>sekretariat.silesia-invest@finanse.pl</t>
+          <t>sekretariat.silesia-invest@onet.pl</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@biuro.pl</t>
+          <t>firma.vistula-fintech@interia.pl</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>kontakt@astra-finance.pl</t>
+          <t>kontakt@o2.pl</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>biuro@ubezpieczenia.pl</t>
+          <t>biuro@proton.me</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>office.helios-markets@broker.local</t>
+          <t>office.helios-markets@brak-domeny</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>kontakt.lumen-advisory@firma.local</t>
+          <t>kontakt.lumen-advisory@yahoo.com</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>biuro.nova-data@nova-data.pl</t>
+          <t>biuro.nova-data@icloud.com</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>sekretariat.optima-trade@biuro.pl</t>
+          <t>sekretariat.optima-trade@gmail.com</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>firma.polaris-capital@kancelaria.pl</t>
+          <t>firma.polaris-capital@wp.pl</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>kontakt@ubezpieczenia.pl</t>
+          <t>kontakt@localhost</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>biuro@silesia-invest.pl</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>office.vistula-fintech@firma.local</t>
+          <t>office.vistula-fintech@o2.pl</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>kontakt.astra-finance@finanse.pl</t>
+          <t>kontakt.astra-finance@proton.me</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>sekretariat.helios-markets@helios-markets.pl</t>
+          <t>sekretariat.helios-markets@outlook.com</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>firma.lumen-advisory@ubezpieczenia.pl</t>
+          <t>firma.lumen-advisory@brak-domeny</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>kontakt@broker.local</t>
+          <t>kontakt@icloud.com</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>biuro@firma.local</t>
+          <t>biuro@gmail.com</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>office.polaris-capital@polaris-capital.pl</t>
+          <t>office.polaris-capital@wp.pl</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>kontakt.quantum-services@biuro.pl</t>
+          <t>kontakt.quantum-services@onet.pl</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>biuro.silesia-invest@kancelaria.pl</t>
+          <t>biuro.silesia-invest@localhost</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@ubezpieczenia.pl</t>
+          <t>sekretariat.vistula-fintech@o2.pl</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>firma.astra-finance@astra-finance.pl</t>
+          <t>firma.astra-finance@proton.me</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>kontakt@firma.local</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>biuro@finanse.pl</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>office.lumen-advisory@biuro.pl</t>
+          <t>office.lumen-advisory@brak-domeny</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>kontakt.nova-data@nova-data.pl</t>
+          <t>kontakt.nova-data@gmail.com</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>biuro.optima-trade@ubezpieczenia.pl</t>
+          <t>biuro.optima-trade@wp.pl</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>sekretariat.polaris-capital@broker.local</t>
+          <t>sekretariat.polaris-capital@onet.pl</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>firma.quantum-services@firma.local</t>
+          <t>firma.quantum-services@interia.pl</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>kontakt@silesia-invest.pl</t>
+          <t>kontakt@localhost</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>biuro@biuro.pl</t>
+          <t>biuro@proton.me</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>office.astra-finance@kancelaria.pl</t>
+          <t>office.astra-finance@outlook.com</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>kontakt.baltic-med-supply@ubezpieczenia.pl</t>
+          <t>kontakt.baltic-med-supply@yahoo.com</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>biuro.helios-markets@helios-markets.pl</t>
+          <t>biuro.helios-markets@@wp.pl</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>sekretariat.lumen-advisory@firma.local</t>
+          <t>sekretariat.lumen-advisory@gmail.com</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>firma.nova-data@finanse.pl</t>
+          <t>firma.nova-data@wp.pl</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>kontakt@biuro.pl</t>
+          <t>kontakt@onet.pl</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>biuro@polaris-capital.pl</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>office.quantum-services@ubezpieczenia.pl</t>
+          <t>office.quantum-services@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>kontakt.silesia-invest@broker.local</t>
+          <t>kontakt.silesia-invest@proton.me</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@firma.local</t>
+          <t>biuro.vistula-fintech@outlook.com</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>sekretariat.astra-finance@astra-finance.pl</t>
+          <t>sekretariat.astra-finance@yahoo.com</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>firma.baltic-med-supply@biuro.pl</t>
+          <t>firma.baltic-med-supply@icloud.com</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>kontakt@kancelaria.pl</t>
+          <t>kontakt@@wp.pl</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>biuro@ubezpieczenia.pl</t>
+          <t>biuro@wp.pl</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>office.nova-data@nova-data.pl</t>
+          <t>office.nova-data@onet.pl</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>kontakt.optima-trade@firma.local</t>
+          <t>kontakt.optima-trade@interia.pl</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>biuro.polaris-capital@finanse.pl</t>
+          <t>biuro.polaris-capital@o2.pl</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>sekretariat.quantum-services@biuro.pl</t>
+          <t>sekretariat.quantum-services@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>firma.silesia-invest@silesia-invest.pl</t>
+          <t>firma.silesia-invest@outlook.com</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>kontakt@ubezpieczenia.pl</t>
+          <t>kontakt@yahoo.com</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>biuro@broker.local</t>
+          <t>biuro@icloud.com</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>office.baltic-med-supply@firma.local</t>
+          <t>office.baltic-med-supply@gmail.com</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>kontakt.helios-markets@helios-markets.pl</t>
+          <t>kontakt.helios-markets@@wp.pl</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>biuro.lumen-advisory@biuro.pl</t>
+          <t>biuro.lumen-advisory@onet.pl</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>sekretariat.nova-data@kancelaria.pl</t>
+          <t>sekretariat.nova-data@interia.pl</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>firma.optima-trade@ubezpieczenia.pl</t>
+          <t>firma.optima-trade@o2.pl</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>kontakt@polaris-capital.pl</t>
+          <t>kontakt@proton.me</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>biuro@firma.local</t>
+          <t>biuro@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>office.silesia-invest@finanse.pl</t>
+          <t>office.silesia-invest@yahoo.com</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@biuro.pl</t>
+          <t>kontakt.vistula-fintech@icloud.com</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>biuro.astra-finance@astra-finance.pl</t>
+          <t>biuro.astra-finance@gmail.com</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>sekretariat.baltic-med-supply@ubezpieczenia.pl</t>
+          <t>sekretariat.baltic-med-supply@wp.pl</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>firma.helios-markets@broker.local</t>
+          <t>firma.helios-markets@@wp.pl</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>kontakt@firma.local</t>
+          <t>kontakt@interia.pl</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>biuro@nova-data.pl</t>
+          <t>biuro@o2.pl</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>office.optima-trade@biuro.pl</t>
+          <t>office.optima-trade@proton.me</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@kancelaria.pl</t>
+          <t>kontakt.polaris-capital@outlook.com</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>biuro.quantum-services@ubezpieczenia.pl</t>
+          <t>biuro.quantum-services@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>sekretariat.silesia-invest@silesia-invest.pl</t>
+          <t>sekretariat.silesia-invest@icloud.com</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@firma.local</t>
+          <t>firma.vistula-fintech@gmail.com</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>kontakt@finanse.pl</t>
+          <t>kontakt@wp.pl</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>biuro@biuro.pl</t>
+          <t>biuro@onet.pl</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>office.helios-markets@helios-markets.pl</t>
+          <t>office.helios-markets@@wp.pl</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>kontakt.lumen-advisory@ubezpieczenia.pl</t>
+          <t>kontakt.lumen-advisory@o2.pl</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>biuro.nova-data@broker.local</t>
+          <t>biuro.nova-data@proton.me</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>sekretariat.optima-trade@firma.local</t>
+          <t>sekretariat.optima-trade@outlook.com</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>firma.polaris-capital@polaris-capital.pl</t>
+          <t>firma.polaris-capital@yahoo.com</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>kontakt@biuro.pl</t>
+          <t>kontakt@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>biuro@kancelaria.pl</t>
+          <t>biuro@gmail.com</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>office.vistula-fintech@ubezpieczenia.pl</t>
+          <t>office.vistula-fintech@wp.pl</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>kontakt.astra-finance@astra-finance.pl</t>
+          <t>kontakt.astra-finance@onet.pl</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>biuro.baltic-med-supply@firma.local</t>
+          <t>biuro.baltic-med-supply@interia.pl</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>sekretariat.helios-markets@finanse.pl</t>
+          <t>sekretariat.helios-markets@@wp.pl</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>firma.lumen-advisory@biuro.pl</t>
+          <t>firma.lumen-advisory@proton.me</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>kontakt@nova-data.pl</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>biuro@ubezpieczenia.pl</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>office.polaris-capital@broker.local</t>
+          <t>office.polaris-capital@icloud.com</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>kontakt.quantum-services@firma.local</t>
+          <t>kontakt.quantum-services@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>biuro.silesia-invest@silesia-invest.pl</t>
+          <t>biuro.silesia-invest@wp.pl</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@biuro.pl</t>
+          <t>sekretariat.vistula-fintech@onet.pl</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>firma.astra-finance@kancelaria.pl</t>
+          <t>firma.astra-finance@interia.pl</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>kontakt@ubezpieczenia.pl</t>
+          <t>kontakt@o2.pl</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>biuro@helios-markets.pl</t>
+          <t>biuro@@wp.pl</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>office.lumen-advisory@firma.local</t>
+          <t>office.lumen-advisory@outlook.com</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>kontakt.nova-data@finanse.pl</t>
+          <t>kontakt.nova-data@yahoo.com</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>biuro.optima-trade@biuro.pl</t>
+          <t>biuro.optima-trade@icloud.com</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>sekretariat.polaris-capital@polaris-capital.pl</t>
+          <t>sekretariat.polaris-capital@gmail.com</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>firma.quantum-services@ubezpieczenia.pl</t>
+          <t>firma.quantum-services@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>kontakt@broker.local</t>
+          <t>kontakt@onet.pl</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>biuro@firma.local</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>office.astra-finance@astra-finance.pl</t>
+          <t>office.astra-finance@o2.pl</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>kontakt.baltic-med-supply@biuro.pl</t>
+          <t>kontakt.baltic-med-supply@proton.me</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>biuro.helios-markets@kancelaria.pl</t>
+          <t>biuro.helios-markets@@wp.pl</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>sekretariat.lumen-advisory@ubezpieczenia.pl</t>
+          <t>sekretariat.lumen-advisory@yahoo.com</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>firma.nova-data@nova-data.pl</t>
+          <t>firma.nova-data@icloud.com</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>kontakt@firma.local</t>
+          <t>kontakt@gmail.com</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>biuro@finanse.pl</t>
+          <t>biuro@wp.pl</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>office.quantum-services@biuro.pl</t>
+          <t>office.quantum-services@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>kontakt.silesia-invest@silesia-invest.pl</t>
+          <t>kontakt.silesia-invest@interia.pl</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@ubezpieczenia.pl</t>
+          <t>biuro.vistula-fintech@o2.pl</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>sekretariat.astra-finance@broker.local</t>
+          <t>sekretariat.astra-finance@proton.me</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>kontakt@helios-markets.pl</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>biuro@biuro.pl</t>
+          <t>biuro@@wp.pl</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>office.nova-data@kancelaria.pl</t>
+          <t>office.nova-data@icloud.com</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>kontakt.optima-trade@ubezpieczenia.pl</t>
+          <t>kontakt.optima-trade@gmail.com</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>biuro.polaris-capital@polaris-capital.pl</t>
+          <t>biuro.polaris-capital@wp.pl</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>sekretariat.quantum-services@firma.local</t>
+          <t>sekretariat.quantum-services@onet.pl</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>firma.silesia-invest@finanse.pl</t>
+          <t>firma.silesia-invest@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>kontakt@biuro.pl</t>
+          <t>kontakt@o2.pl</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>biuro@astra-finance.pl</t>
+          <t>biuro@proton.me</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>office.baltic-med-supply@ubezpieczenia.pl</t>
+          <t>office.baltic-med-supply@outlook.com</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>kontakt.helios-markets@broker.local</t>
+          <t>kontakt.helios-markets@yahoo.com</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>biuro.lumen-advisory@firma.local</t>
+          <t>biuro.lumen-advisory@@wp.pl</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>sekretariat.nova-data@nova-data.pl</t>
+          <t>sekretariat.nova-data@gmail.com</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>firma.optima-trade@biuro.pl</t>
+          <t>firma.optima-trade@wp.pl</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>kontakt@kancelaria.pl</t>
+          <t>kontakt@onet.pl</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>biuro@ubezpieczenia.pl</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>office.silesia-invest@silesia-invest.pl</t>
+          <t>office.silesia-invest@mail_invalid.pl</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@firma.local</t>
+          <t>kontakt.vistula-fintech@proton.me</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>biuro.astra-finance@finanse.pl</t>
+          <t>biuro.astra-finance@outlook.com</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>sekretariat.baltic-med-supply@biuro.pl</t>
+          <t>sekretariat.baltic-med-supply@yahoo.com</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>firma.helios-markets@helios-markets.pl</t>
+          <t>firma.helios-markets.gmail.com</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>kontakt@ubezpieczenia.pl</t>
+          <t>kontakt@gmail.com</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>biuro@broker.local</t>
+          <t>biuro@wp.pl</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>office.optima-trade@firma.local</t>
+          <t>office.optima-trade@onet.pl</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@polaris-capital.pl</t>
+          <t>kontakt.polaris-capital@interia.pl</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>biuro.quantum-services@biuro.pl</t>
+          <t>biuro.quantum-services@nieistniejaca-domena</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>sekretariat.silesia-invest@kancelaria.pl</t>
+          <t>sekretariat.silesia-invest@proton.me</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@ubezpieczenia.pl</t>
+          <t>firma.vistula-fintech@outlook.com</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>kontakt@astra-finance.pl</t>
+          <t>kontakt@yahoo.com</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>biuro@firma.local</t>
+          <t>biuro@icloud.com</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>office.helios-markets@finanse.pl</t>
+          <t>office.helios-markets.gmail.com</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>kontakt.lumen-advisory@biuro.pl</t>
+          <t>kontakt.lumen-advisory@wp.pl</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>biuro.nova-data@nova-data.pl</t>
+          <t>biuro.nova-data@onet.pl</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>sekretariat.optima-trade@ubezpieczenia.pl</t>
+          <t>sekretariat.optima-trade@interia.pl</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>firma.polaris-capital@broker.local</t>
+          <t>firma.polaris-capital@o2.pl</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>kontakt@firma.local</t>
+          <t>kontakt@nieistniejaca-domena</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>biuro@silesia-invest.pl</t>
+          <t>biuro@outlook.com</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>office.vistula-fintech@biuro.pl</t>
+          <t>office.vistula-fintech@yahoo.com</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>kontakt.astra-finance@kancelaria.pl</t>
+          <t>kontakt.astra-finance@icloud.com</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>biuro.baltic-med-supply@ubezpieczenia.pl</t>
+          <t>biuro.baltic-med-supply@gmail.com</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>sekretariat.helios-markets@helios-markets.pl</t>
+          <t>sekretariat.helios-markets.gmail.com</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>firma.lumen-advisory@firma.local</t>
+          <t>firma.lumen-advisory@onet.pl</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>kontakt@finanse.pl</t>
+          <t>kontakt@interia.pl</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>biuro@biuro.pl</t>
+          <t>biuro@o2.pl</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>office.polaris-capital@polaris-capital.pl</t>
+          <t>office.polaris-capital@proton.me</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>kontakt.quantum-services@ubezpieczenia.pl</t>
+          <t>kontakt.quantum-services@nieistniejaca-domena</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>biuro.silesia-invest@broker.local</t>
+          <t>biuro.silesia-invest@yahoo.com</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@firma.local</t>
+          <t>sekretariat.vistula-fintech@icloud.com</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>firma.astra-finance@astra-finance.pl</t>
+          <t>firma.astra-finance@gmail.com</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>kontakt@biuro.pl</t>
+          <t>kontakt@wp.pl</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>biuro@kancelaria.pl</t>
+          <t>biuro.gmail.com</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>office.lumen-advisory@ubezpieczenia.pl</t>
+          <t>office.lumen-advisory@interia.pl</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>kontakt.nova-data@nova-data.pl</t>
+          <t>kontakt.nova-data@o2.pl</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>biuro.optima-trade@firma.local</t>
+          <t>biuro.optima-trade@proton.me</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>sekretariat.polaris-capital@finanse.pl</t>
+          <t>sekretariat.polaris-capital@outlook.com</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>firma.quantum-services@biuro.pl</t>
+          <t>firma.quantum-services@nieistniejaca-domena</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>kontakt@silesia-invest.pl</t>
+          <t>kontakt@icloud.com</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>biuro@ubezpieczenia.pl</t>
+          <t>biuro@gmail.com</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>office.astra-finance@broker.local</t>
+          <t>office.astra-finance@wp.pl</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>kontakt.baltic-med-supply@firma.local</t>
+          <t>kontakt.baltic-med-supply@onet.pl</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>biuro.helios-markets@helios-markets.pl</t>
+          <t>biuro.helios-markets.gmail.com</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>sekretariat.lumen-advisory@biuro.pl</t>
+          <t>sekretariat.lumen-advisory@o2.pl</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>firma.nova-data@kancelaria.pl</t>
+          <t>firma.nova-data@proton.me</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>kontakt@ubezpieczenia.pl</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>biuro@polaris-capital.pl</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>office.quantum-services@firma.local</t>
+          <t>office.quantum-services@nieistniejaca-domena</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>kontakt.silesia-invest@finanse.pl</t>
+          <t>kontakt.silesia-invest@gmail.com</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@biuro.pl</t>
+          <t>biuro.vistula-fintech@wp.pl</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">

--- a/data/xlsx/regon.xlsx
+++ b/data/xlsx/regon.xlsx
@@ -185,7 +185,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>biuro@onet.pl</t>
+          <t>biuro@bbb.ii</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -272,7 +272,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>office.baltic-med-supply@interia.pl</t>
+          <t>office.baltic-med-supply@mmm.zz</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -359,7 +359,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>kontakt.helios-markets@brak-domeny</t>
+          <t>kontakt.helios-markets@nnn.yy</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>biuro.lumen-advisory@proton.me</t>
+          <t>biuro.lumen-advisory@kkk.uu</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>sekretariat.nova-data@outlook.com</t>
+          <t>sekretariat.nova-data@tmp.ii</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>firma.optima-trade@yahoo.com</t>
+          <t>firma.optima-trade@foo.zz</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>kontakt@icloud.com</t>
+          <t>kontakt@bar.yy</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>biuro@localhost</t>
+          <t>biuro@zzz.uu</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>office.silesia-invest@wp.pl</t>
+          <t>office.silesia-invest@yahoo.com</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@onet.pl</t>
+          <t>kontakt.vistula-fintech@icloud.com</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>biuro.astra-finance@interia.pl</t>
+          <t>biuro.astra-finance@gmail.com</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sekretariat.baltic-med-supply@o2.pl</t>
+          <t>sekretariat.baltic-med-supply@wp.pl</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>firma.helios-markets@brak-domeny</t>
+          <t>firma.helios-markets@onet.pl</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>kontakt@outlook.com</t>
+          <t>kontakt@interia.pl</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>biuro@yahoo.com</t>
+          <t>biuro@o2.pl</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>office.optima-trade@icloud.com</t>
+          <t>office.optima-trade@proton.me</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@gmail.com</t>
+          <t>kontakt.polaris-capital@outlook.com</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>biuro.quantum-services@localhost</t>
+          <t>biuro.quantum-services@yahoo.com</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>sekretariat.silesia-invest@onet.pl</t>
+          <t>sekretariat.silesia-invest@icloud.com</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@interia.pl</t>
+          <t>firma.vistula-fintech@gmail.com</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>kontakt@o2.pl</t>
+          <t>kontakt@wp.pl</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>biuro@proton.me</t>
+          <t>biuro@onet.pl</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>office.helios-markets@brak-domeny</t>
+          <t>office.helios-markets@interia.pl</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>kontakt.lumen-advisory@yahoo.com</t>
+          <t>kontakt.lumen-advisory@o2.pl</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>biuro.nova-data@icloud.com</t>
+          <t>biuro.nova-data@proton.me</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>sekretariat.optima-trade@gmail.com</t>
+          <t>sekretariat.optima-trade@outlook.com</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>firma.polaris-capital@wp.pl</t>
+          <t>firma.polaris-capital@yahoo.com</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>kontakt@localhost</t>
+          <t>kontakt@icloud.com</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>biuro@interia.pl</t>
+          <t>biuro@gmail.com</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>office.vistula-fintech@o2.pl</t>
+          <t>office.vistula-fintech@wp.pl</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>kontakt.astra-finance@proton.me</t>
+          <t>kontakt.astra-finance@onet.pl</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>biuro.baltic-med-supply@biuropl</t>
+          <t>biuro.baltic-med-supply@interia.pl</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>sekretariat.helios-markets@outlook.com</t>
+          <t>sekretariat.helios-markets@o2.pl</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>firma.lumen-advisory@brak-domeny</t>
+          <t>firma.lumen-advisory@proton.me</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>kontakt@icloud.com</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>biuro@gmail.com</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>office.polaris-capital@wp.pl</t>
+          <t>office.polaris-capital@icloud.com</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>kontakt.quantum-services@onet.pl</t>
+          <t>kontakt.quantum-services@gmail.com</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>biuro.silesia-invest@localhost</t>
+          <t>biuro.silesia-invest@wp.pl</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@o2.pl</t>
+          <t>sekretariat.vistula-fintech@onet.pl</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>firma.astra-finance@proton.me</t>
+          <t>firma.astra-finance@interia.pl</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>kontakt@outlook.com</t>
+          <t>kontakt@o2.pl</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>biuro@yahoo.com</t>
+          <t>biuro@proton.me</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>office.lumen-advisory@brak-domeny</t>
+          <t>office.lumen-advisory@outlook.com</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>kontakt.nova-data@gmail.com</t>
+          <t>kontakt.nova-data@yahoo.com</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>biuro.optima-trade@wp.pl</t>
+          <t>biuro.optima-trade@icloud.com</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>sekretariat.polaris-capital@onet.pl</t>
+          <t>sekretariat.polaris-capital@gmail.com</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>firma.quantum-services@interia.pl</t>
+          <t>firma.quantum-services@wp.pl</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>kontakt@localhost</t>
+          <t>kontakt@onet.pl</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>biuro@proton.me</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>office.astra-finance@outlook.com</t>
+          <t>office.astra-finance@o2.pl</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>kontakt.baltic-med-supply@yahoo.com</t>
+          <t>kontakt.baltic-med-supply@proton.me</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>biuro.helios-markets@@wp.pl</t>
+          <t>biuro.helios-markets@outlook.com</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>sekretariat.lumen-advisory@gmail.com</t>
+          <t>sekretariat.lumen-advisory@yahoo.com</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>firma.nova-data@wp.pl</t>
+          <t>firma.nova-data@icloud.com</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>kontakt@onet.pl</t>
+          <t>kontakt@gmail.com</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>biuro@interia.pl</t>
+          <t>biuro@wp.pl</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>office.quantum-services@mail_invalid.pl</t>
+          <t>office.quantum-services@onet.pl</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>kontakt.silesia-invest@proton.me</t>
+          <t>kontakt.silesia-invest@interia.pl</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@outlook.com</t>
+          <t>biuro.vistula-fintech@o2.pl</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>sekretariat.astra-finance@yahoo.com</t>
+          <t>sekretariat.astra-finance@proton.me</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>firma.baltic-med-supply@icloud.com</t>
+          <t>firma.baltic-med-supply@outlook.com</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>kontakt@@wp.pl</t>
+          <t>kontakt@yahoo.com</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>biuro@wp.pl</t>
+          <t>biuro@icloud.com</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>office.nova-data@onet.pl</t>
+          <t>office.nova-data@gmail.com</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>kontakt.optima-trade@interia.pl</t>
+          <t>kontakt.optima-trade@wp.pl</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>biuro.polaris-capital@o2.pl</t>
+          <t>biuro.polaris-capital@onet.pl</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>sekretariat.quantum-services@mail_invalid.pl</t>
+          <t>sekretariat.quantum-services@interia.pl</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>firma.silesia-invest@outlook.com</t>
+          <t>firma.silesia-invest@o2.pl</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>kontakt@yahoo.com</t>
+          <t>kontakt@proton.me</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>biuro@icloud.com</t>
+          <t>biuro@outlook.com</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>office.baltic-med-supply@gmail.com</t>
+          <t>office.baltic-med-supply@yahoo.com</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>kontakt.helios-markets@@wp.pl</t>
+          <t>kontakt.helios-markets@icloud.com</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>biuro.lumen-advisory@onet.pl</t>
+          <t>biuro.lumen-advisory@gmail.com</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>sekretariat.nova-data@interia.pl</t>
+          <t>sekretariat.nova-data@wp.pl</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>firma.optima-trade@o2.pl</t>
+          <t>firma.optima-trade@onet.pl</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>kontakt@proton.me</t>
+          <t>kontakt@interia.pl</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>biuro@mail_invalid.pl</t>
+          <t>biuro@o2.pl</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>office.silesia-invest@yahoo.com</t>
+          <t>office.silesia-invest@proton.me</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@icloud.com</t>
+          <t>kontakt.vistula-fintech@outlook.com</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>biuro.astra-finance@gmail.com</t>
+          <t>biuro.astra-finance@yahoo.com</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>sekretariat.baltic-med-supply@wp.pl</t>
+          <t>sekretariat.baltic-med-supply@icloud.com</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>firma.helios-markets@@wp.pl</t>
+          <t>firma.helios-markets@gmail.com</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>kontakt@interia.pl</t>
+          <t>kontakt@wp.pl</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>biuro@o2.pl</t>
+          <t>biuro@onet.pl</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>office.optima-trade@proton.me</t>
+          <t>office.optima-trade@interia.pl</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@outlook.com</t>
+          <t>kontakt.polaris-capital@o2.pl</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>biuro.quantum-services@mail_invalid.pl</t>
+          <t>biuro.quantum-services@proton.me</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>sekretariat.silesia-invest@icloud.com</t>
+          <t>sekretariat.silesia-invest@outlook.com</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@gmail.com</t>
+          <t>firma.vistula-fintech@yahoo.com</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>kontakt@wp.pl</t>
+          <t>kontakt@icloud.com</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>biuro@onet.pl</t>
+          <t>biuro@gmail.com</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>office.helios-markets@@wp.pl</t>
+          <t>office.helios-markets@wp.pl</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>kontakt.lumen-advisory@o2.pl</t>
+          <t>kontakt.lumen-advisory@onet.pl</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>biuro.nova-data@proton.me</t>
+          <t>biuro.nova-data@interia.pl</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>sekretariat.optima-trade@outlook.com</t>
+          <t>sekretariat.optima-trade@o2.pl</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>firma.polaris-capital@yahoo.com</t>
+          <t>firma.polaris-capital@proton.me</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>kontakt@mail_invalid.pl</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>biuro@gmail.com</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>office.vistula-fintech@wp.pl</t>
+          <t>office.vistula-fintech@icloud.com</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>kontakt.astra-finance@onet.pl</t>
+          <t>kontakt.astra-finance@foo.zz</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>biuro.baltic-med-supply@interia.pl</t>
+          <t>biuro.baltic-med-supply@bar.yy</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>sekretariat.helios-markets@@wp.pl</t>
+          <t>sekretariat.helios-markets@zzz.uu</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>firma.lumen-advisory@proton.me</t>
+          <t>firma.lumen-advisory@uuu.ii</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>kontakt@outlook.com</t>
+          <t>kontakt@qqq.zz</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>biuro@yahoo.com</t>
+          <t>biuro@abc.yy</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>office.polaris-capital@icloud.com</t>
+          <t>office.polaris-capital@xxx.uu</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>kontakt.quantum-services@mail_invalid.pl</t>
+          <t>kontakt.quantum-services@bbb.ii</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>biuro.silesia-invest@wp.pl</t>
+          <t>biuro.silesia-invest@icloud.com</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@onet.pl</t>
+          <t>sekretariat.vistula-fintech@gmail.com</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>firma.astra-finance@interia.pl</t>
+          <t>firma.astra-finance@wp.pl</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>kontakt@o2.pl</t>
+          <t>kontakt@onet.pl</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>biuro@@wp.pl</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>office.lumen-advisory@outlook.com</t>
+          <t>office.lumen-advisory@o2.pl</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>kontakt.nova-data@yahoo.com</t>
+          <t>kontakt.nova-data@proton.me</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>biuro.optima-trade@icloud.com</t>
+          <t>biuro.optima-trade@outlook.com</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>sekretariat.polaris-capital@gmail.com</t>
+          <t>sekretariat.polaris-capital@yahoo.com</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>firma.quantum-services@mail_invalid.pl</t>
+          <t>firma.quantum-services@icloud.com</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>kontakt@onet.pl</t>
+          <t>kontakt@gmail.com</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>biuro@interia.pl</t>
+          <t>biuro@wp.pl</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>office.astra-finance@o2.pl</t>
+          <t>office.astra-finance@onet.pl</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>kontakt.baltic-med-supply@proton.me</t>
+          <t>kontakt.baltic-med-supply@interia.pl</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>biuro.helios-markets@@wp.pl</t>
+          <t>biuro.helios-markets@o2.pl</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>sekretariat.lumen-advisory@yahoo.com</t>
+          <t>sekretariat.lumen-advisory@proton.me</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>firma.nova-data@icloud.com</t>
+          <t>firma.nova-data@outlook.com</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>kontakt@gmail.com</t>
+          <t>kontakt@yahoo.com</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>biuro@wp.pl</t>
+          <t>biuro@icloud.com</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>office.quantum-services@mail_invalid.pl</t>
+          <t>office.quantum-services@gmail.com</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>kontakt.silesia-invest@interia.pl</t>
+          <t>kontakt.silesia-invest@wp.pl</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@o2.pl</t>
+          <t>biuro.vistula-fintech@onet.pl</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>sekretariat.astra-finance@proton.me</t>
+          <t>sekretariat.astra-finance@interia.pl</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>firma.baltic-med-supplyfirma.local</t>
+          <t>firma.baltic-med-supplyfirma.local@o2.pl</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>kontakt@outlook.com</t>
+          <t>kontakt@proton.me</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>biuro@@wp.pl</t>
+          <t>biuro@outlook.com</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>office.nova-data@icloud.com</t>
+          <t>office.nova-data@yahoo.com</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>kontakt.optima-trade@gmail.com</t>
+          <t>kontakt.optima-trade@icloud.com</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>biuro.polaris-capital@wp.pl</t>
+          <t>biuro.polaris-capital@gmail.com</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>sekretariat.quantum-services@onet.pl</t>
+          <t>sekretariat.quantum-services@wp.pl</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>firma.silesia-invest@mail_invalid.pl</t>
+          <t>firma.silesia-invest@onet.pl</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>kontakt@o2.pl</t>
+          <t>kontakt@interia.pl</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>biuro@proton.me</t>
+          <t>biuro@o2.pl</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>office.baltic-med-supply@outlook.com</t>
+          <t>office.baltic-med-supply@proton.me</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>kontakt.helios-markets@yahoo.com</t>
+          <t>kontakt.helios-markets@outlook.com</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>biuro.lumen-advisory@@wp.pl</t>
+          <t>biuro.lumen-advisory@yahoo.com</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>sekretariat.nova-data@gmail.com</t>
+          <t>sekretariat.nova-data@icloud.com</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>firma.optima-trade@wp.pl</t>
+          <t>firma.optima-trade@gmail.com</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>kontakt@onet.pl</t>
+          <t>kontakt@wp.pl</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>biuro@interia.pl</t>
+          <t>biuro@onet.pl</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>office.silesia-invest@mail_invalid.pl</t>
+          <t>office.silesia-invest@interia.pl</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@proton.me</t>
+          <t>kontakt.vistula-fintech@o2.pl</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>biuro.astra-finance@outlook.com</t>
+          <t>biuro.astra-finance@proton.me</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>sekretariat.baltic-med-supply@yahoo.com</t>
+          <t>sekretariat.baltic-med-supply@outlook.com</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>firma.helios-markets.gmail.com</t>
+          <t>firma.helios-markets.gmail.com@yahoo.com</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>kontakt@gmail.com</t>
+          <t>kontakt@icloud.com</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>biuro@wp.pl</t>
+          <t>biuro@gmail.com</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>office.optima-trade@onet.pl</t>
+          <t>office.optima-trade@wp.pl</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@interia.pl</t>
+          <t>kontakt.polaris-capital@onet.pl</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>biuro.quantum-services@nieistniejaca-domena</t>
+          <t>biuro.quantum-services@interia.pl</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>sekretariat.silesia-invest@proton.me</t>
+          <t>sekretariat.silesia-invest@o2.pl</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@outlook.com</t>
+          <t>firma.vistula-fintech@proton.me</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>kontakt@yahoo.com</t>
+          <t>kontakt@outlook.com</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>biuro@icloud.com</t>
+          <t>biuro@yahoo.com</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>office.helios-markets.gmail.com</t>
+          <t>office.helios-markets.gmail.com@icloud.com</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>kontakt.lumen-advisory@wp.pl</t>
+          <t>kontakt.lumen-advisory@gmail.com</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>biuro.nova-data@onet.pl</t>
+          <t>biuro.nova-data@wp.pl</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>sekretariat.optima-trade@interia.pl</t>
+          <t>sekretariat.optima-trade@onet.pl</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>firma.polaris-capital@o2.pl</t>
+          <t>firma.polaris-capital@interia.pl</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>kontakt@nieistniejaca-domena</t>
+          <t>kontakt@o2.pl</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>biuro@outlook.com</t>
+          <t>biuro@proton.me</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>office.vistula-fintech@yahoo.com</t>
+          <t>office.vistula-fintech@outlook.com</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>kontakt.astra-finance@icloud.com</t>
+          <t>kontakt.astra-finance@yahoo.com</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>biuro.baltic-med-supply@gmail.com</t>
+          <t>biuro.baltic-med-supply@icloud.com</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>sekretariat.helios-markets.gmail.com</t>
+          <t>sekretariat.helios-markets.gmail.com@gmail.com</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>firma.lumen-advisory@onet.pl</t>
+          <t>firma.lumen-advisory@wp.pl</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>kontakt@interia.pl</t>
+          <t>kontakt@onet.pl</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>biuro@o2.pl</t>
+          <t>biuro@interia.pl</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>office.polaris-capital@proton.me</t>
+          <t>office.polaris-capital@o2.pl</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>kontakt.quantum-services@nieistniejaca-domena</t>
+          <t>kontakt.quantum-services@proton.me</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>biuro.silesia-invest@yahoo.com</t>
+          <t>biuro.silesia-invest@outlook.com</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@icloud.com</t>
+          <t>sekretariat.vistula-fintech@yahoo.com</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>firma.astra-finance@gmail.com</t>
+          <t>firma.astra-finance@icloud.com</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>kontakt@wp.pl</t>
+          <t>kontakt@gmail.com</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>biuro.gmail.com</t>
+          <t>biuro.gmail.com@wp.pl</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>office.lumen-advisory@interia.pl</t>
+          <t>office.lumen-advisory@onet.pl</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>kontakt.nova-data@o2.pl</t>
+          <t>kontakt.nova-data@interia.pl</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>biuro.optima-trade@proton.me</t>
+          <t>biuro.optima-trade@o2.pl</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>sekretariat.polaris-capital@outlook.com</t>
+          <t>sekretariat.polaris-capital@proton.me</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>firma.quantum-services@nieistniejaca-domena</t>
+          <t>firma.quantum-services@outlook.com</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>kontakt@icloud.com</t>
+          <t>kontakt@yahoo.com</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>biuro@gmail.com</t>
+          <t>biuro@icloud.com</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>office.astra-finance@wp.pl</t>
+          <t>office.astra-finance@gmail.com</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>kontakt.baltic-med-supply@onet.pl</t>
+          <t>kontakt.baltic-med-supply@wp.pl</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>biuro.helios-markets.gmail.com</t>
+          <t>biuro.helios-markets.gmail.com@onet.pl</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>sekretariat.lumen-advisory@o2.pl</t>
+          <t>sekretariat.lumen-advisory@interia.pl</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>firma.nova-data@proton.me</t>
+          <t>firma.nova-data@o2.pl</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>kontakt@outlook.com</t>
+          <t>kontakt@proton.me</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>biuro@yahoo.com</t>
+          <t>biuro@outlook.com</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>office.quantum-services@nieistniejaca-domena</t>
+          <t>office.quantum-services@yahoo.com</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>kontakt.silesia-invest@gmail.com</t>
+          <t>kontakt.silesia-invest@icloud.com</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@wp.pl</t>
+          <t>biuro.vistula-fintech@gmail.com</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">

--- a/data/xlsx/regon.xlsx
+++ b/data/xlsx/regon.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Quantum Servicse S.A.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>235676557</t>
+          <t>335676557</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0000001948</t>
+          <t>000000194</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2236468458</t>
+          <t>1236468458</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>office.quantum-services@onet.pl</t>
+          <t>office.quantum-services@onetpl</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>firma.baltic-med-supply@yahoocom</t>
+          <t>firma.baltic-med-supply@yahoo.com</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>000000350</t>
+          <t>0000003500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3513,7 +3513,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>338052254</t>
+          <t>238052254</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>biuro@gmail.com</t>
+          <t>biuro@finanse24.xs</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>2238289820</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>kontakt.vistula-fintech@finanse24.xs</t>
+          <t>kontakt.vistula-fintech@outlook.com</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Qunatum Services sp. z o. o.</t>
+          <t>Quantum Services sp. z o. o.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>wałsnśoć prywatna rk</t>
+          <t>własnśoć prywatna r</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5166,7 +5166,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>239556867</t>
+          <t>339556867</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0000006798</t>
+          <t>000000679</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2240427951</t>
+          <t>1240427951</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7264,47 +7264,47 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>0000007962</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>sp z oo</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>własność prywatna krajowa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LUBELSKIE</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>LUBLIN</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>LUBLIN</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t/>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>sp z oo</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>własność prywatna krajowa</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>LUBELSKIE</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>LUBLIN</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>LUBLIN</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>LUBLIN</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>000000835</t>
+          <t>0000008350</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7863,7 +7863,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>342090949</t>
+          <t>242090949</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>biuro@outlook.com</t>
+          <t>biuro@ubezpiecznia.pl</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1242249324</t>
+          <t>2242249324</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>biuro.vistula-fintech@ubezpiecznia.pl</t>
+          <t>biuro.vistula-fintech@onet.pl</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>243278796</t>
+          <t/>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9342,7 +9342,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t/>
+          <t>243357981</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9429,7 +9429,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>243437177</t>
+          <t>343437177</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>uQantum Services SA</t>
+          <t>Quantum Services SA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t/>
+          <t>0000010872</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0000011066</t>
+          <t/>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0000011648</t>
+          <t>000001164</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2244387450</t>
+          <t>1244387450</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>kontakt.polaris-capital@proton.me</t>
+          <t>kontakt.polaris-capitalproton.me</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>biuroonet.pl</t>
+          <t>biuro@onet.pl</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>000001310</t>
+          <t>0000013103</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>biuro@wp.pl</t>
+          <t>biuro@abxza.pl</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -12213,7 +12213,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>345971254</t>
+          <t>245971254</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>2246288019</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>sekretariat.vistula-fintech@abxza.pl</t>
+          <t>sekretariat.vistula-fintech@o2.pl</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -13692,7 +13692,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>247317487</t>
+          <t>347317487</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Qunatum Services Sp. z o.o.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>wałsnoćś prywatan krajowa</t>
+          <t>wasłność prywatan krajowa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0000016498</t>
+          <t>000001649</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2248346956</t>
+          <t>1248346956</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>000001785</t>
+          <t>0000017856</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>biuro@onet.pl</t>
+          <t>biuro@uuu.xs</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -16563,7 +16563,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>350009941</t>
+          <t>250009941</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1250168327</t>
+          <t>2250168327</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>firma.vistula-fintech@uuu.xs</t>
+          <t>firma.vistula-fintech@yahoo.com</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">

--- a/data/xlsx/regon.xlsx
+++ b/data/xlsx/regon.xlsx
@@ -222,7 +222,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -272,12 +272,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>office.zielony-bieszczady@outlook.com</t>
+          <t>office.pewny-delfin@outlook.com</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://zielony-bieszczady.eu</t>
+          <t>https://pewny-delfin.eu</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -309,7 +309,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -359,12 +359,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>kontakt.zielony-karpaty@wp.pl</t>
+          <t>kontakt.dobry-koral@wp.pl</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.zielony-karpaty-group.local</t>
+          <t>https://www.dobry-koral-group.local</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -396,7 +396,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -446,12 +446,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>biuro.zielony-baltyk@onet.pl</t>
+          <t>biuro.polski-szafir@onet.pl</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.zielony-baltyk-group.pl</t>
+          <t>https://www.polski-szafir-group.pl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -533,12 +533,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>sekretariat.zielony-sudety@interia.pl</t>
+          <t>sekretariat.europejski-orzel@interia.pl</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.zielony-sudety-group.com.pl</t>
+          <t>https://www.europejski-orzel-group.com.pl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>firma.niebieski-amber@o2.pl</t>
+          <t>firma.globalny-kaktus@o2.pl</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://www.niebieski-amber.eu</t>
+          <t>https://www.globalny-kaktus.eu</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BIAŁSYTOK</t>
+          <t>BIAŁYSTOK</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.niebieski-canyon-group.pl</t>
+          <t>https://www.nowoczesny-beskid-group.pl</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>office.niebieski-delfin@gmail.com</t>
+          <t>office.tradycyjny-canyon@gmail.com</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.niebieski-delfin-group.com.pl</t>
+          <t>https://www.tradycyjny-canyon-group.com.pl</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>kontakt.niebieski-echo@outlook.com</t>
+          <t>kontakt.dynamiczny-jantar@outlook.com</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://www.niebieski-echo-group.eu</t>
+          <t>https://www.dynamiczny-jantar-group.eu</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>biuro.niebieski-falcon@wp.pl</t>
+          <t>biuro.stabilny-rubin@wp.pl</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://www.niebieski-falcon.local</t>
+          <t>https://www.stabilny-rubin.local</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sekretariat.niebieski-gryf@onet.pl</t>
+          <t>sekretariat.innowacyjny-sokol@onet.pl</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://niebieski-gryf.pl</t>
+          <t>https://innowacyjny-sokol.pl</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>firma.niebieski-horyzont@interia.pl</t>
+          <t>firma.kreatywny-jodelka@interia.pl</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.niebieski-ikar-group.eu</t>
+          <t>https://www.aktywny-zodiak-group.eu</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://www.niebieski-jantar-group.local</t>
+          <t>https://www.jasny-kasprowy-group.local</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>office.niebieski-koral@yahoo.com</t>
+          <t>office.green-bizon@yahoo.com</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://www.niebieski-koral.pl</t>
+          <t>https://www.green-bizon.pl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>kontakt.niebieski-lotos@gmail.com</t>
+          <t>kontakt.blue-ikar@gmail.com</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://niebieski-lotos.com.pl</t>
+          <t>https://blue-ikar.com.pl</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1659,17 +1659,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>642892372</t>
+          <t/>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>biuro.niebieski-magnolia@outlook.com</t>
+          <t>biuro.gold-pegaz@outlook.com</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://www.niebieski-magnolia-group.eu</t>
+          <t>https://www.gold-pegaz-group.eu</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>sekretariat.niebieski-neon@wp.pl</t>
+          <t>sekretariat.silver-zubr@wp.pl</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>firma.niebieski-oaza@onet.pl</t>
+          <t>firma.smart-narew@onet.pl</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://www.niebieski-oaza-group.pl</t>
+          <t>https://www.smart-narew-group.pl</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://www.niebieski-pegaz.com.pl</t>
+          <t>https://www.fast-syrena.com.pl</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://niebieski-rubin.eu</t>
+          <t>https://safe-rysy.eu</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>office.niebieski-szafir@proton.me</t>
+          <t>office.best-amber@proton.me</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://www.niebieski-szafir-group.local</t>
+          <t>https://www.best-amber-group.local</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>kontakt.niebieski-tytan@yahoo.com</t>
+          <t>kontakt.global-horyzont@yahoo.com</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://www.niebieski-tytan-group.pl</t>
+          <t>https://www.global-horyzont-group.pl</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>biuro.niebieski-uran@gmail.com</t>
+          <t>biuro.future-oaza@gmail.com</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>sekretariat.niebieski-wektor@outlook.com</t>
+          <t>sekretariat.wielkopolski-zefir@outlook.com</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://www.niebieski-wektor.eu</t>
+          <t>https://www.wielkopolski-zefir.eu</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>firma.niebieski-zefir@wp.pl</t>
+          <t>firma.slaski-pilica@wp.pl</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://niebieski-zefir.local</t>
+          <t>https://slaski-pilica.local</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://www.niebieski-zubr-group.pl</t>
+          <t>https://www.mazowiecki-marmur-group.pl</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://www.niebieski-sokol-group.com.pl</t>
+          <t>https://www.pomorski-giewont-group.com.pl</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>office.niebieski-orzel@o2.pl</t>
+          <t>office.dolnoslaski-sudety@o2.pl</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://www.niebieski-orzel-group.eu</t>
+          <t>https://www.dolnoslaski-sudety-group.eu</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>kontakt.niebieski-kormoran@proton.me</t>
+          <t>kontakt.karpacki-gryf@proton.me</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>biuro.niebieski-barycz@yahoocom</t>
+          <t>biuro.baltycki-neon@yahoocom</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://niebieski-barycz.pl</t>
+          <t>https://baltycki-neon.pl</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>sekretariat.niebieski-notec@gmail.com</t>
+          <t>sekretariat.mlody-wektor@gmail.com</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://www.niebieski-notec-group.com.pl</t>
+          <t>https://www.mlody-wektor-group.com.pl</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>firma.niebieski-pilica@outlook.com</t>
+          <t>firma.wspolny-notec@outlook.com</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://www.niebieski-pilica-group.eu</t>
+          <t>https://www.wspolny-notec-group.eu</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://www.niebieski-narew-group.local</t>
+          <t>https://www.pierwszy-granit-group.local</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://www.niebieski-jodelka.pl</t>
+          <t>https://www.zielony-zubr.pl</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>office.niebieski-kaktus@interia.pl</t>
+          <t>office.niebieski-narew@interia.pl</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>kontakt.niebieski-szmaragd@o2.pl</t>
+          <t>kontakt.zloty-syrena@o2.pl</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://www.niebieski-szmaragd-group.eu</t>
+          <t>https://www.zloty-syrena-group.eu</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>biuro.niebieski-topaz@proton.me</t>
+          <t>biuro.srebrny-rysy@proton.me</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://www.niebieski-topaz-group.local</t>
+          <t>https://www.srebrny-rysy-group.local</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>sekretariat.niebieski-granit@yahoo.com</t>
+          <t>sekretariat.czysty-amber@yahoo.com</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://www.niebieski-granit-group.pl</t>
+          <t>https://www.czysty-amber-group.pl</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://niebieski-syrena.eu</t>
+          <t>https://pewny-oaza.eu</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>office.niebieski-olimp@onet.pl</t>
+          <t>office.polski-pilica@onet.pl</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://www.niebieski-olimp-group.pl</t>
+          <t>https://www.polski-pilica-group.pl</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>kontakt.niebieski-zorza@interia.pl</t>
+          <t>kontakt.europejski-marmur@interia.pl</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>https://www.niebieski-zorza-group.com.pl</t>
+          <t>https://www.europejski-marmur-group.com.pl</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>biuro.niebieski-krokus@o2.pl</t>
+          <t>biuro.globalny-giewont@o2.pl</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://www.niebieski-krokus.eu</t>
+          <t>https://www.globalny-giewont.eu</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>sekretariat.niebieski-narcyz@proton.me</t>
+          <t>sekretariat.lokalny-sudety@proton.me</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://niebieski-narcyz.local</t>
+          <t>https://lokalny-sudety.local</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>firma.niebieski-giewont@yahoo.com</t>
+          <t>firma.nowoczesny-gryf@yahoo.com</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://www.niebieski-giewont-group.pl</t>
+          <t>https://www.nowoczesny-gryf-group.pl</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://www.niebieski-kasprowy-group.eu</t>
+          <t>https://www.dynamiczny-wektor-group.eu</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>kontakt.amber-transport@onet.pl</t>
+          <t>kontakt.falcon-transport@onet.pl</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://amber-transport.pl</t>
+          <t>https://falcon-transport.pl</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>biuro.amber-spedycja@interia.pl</t>
+          <t>biuro.koral-spedycja@interia.pl</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>https://www.amber-spedycja-group.com.pl</t>
+          <t>https://www.koral-spedycja-group.com.pl</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>sekretariat.amber-logistyka@o2.pl</t>
+          <t>sekretariat.pegaz-logistyka@o2.pl</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://www.amber-logistyka-group.eu</t>
+          <t>https://www.pegaz-logistyka-group.eu</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>firma.amber-handel@proton.me</t>
+          <t>firma.wektor-handel@proton.me</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>https://www.amber-uslugi.pl</t>
+          <t>https://www.kormoran-uslugi.pl</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://amber-finanse.com.pl</t>
+          <t>https://jodelka-finanse.com.pl</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>własnśoć prywatna rk</t>
+          <t>własnśoć prywtana rk</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>IZELONA GÓRA</t>
+          <t>ZIELONA GÓRA</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>office.amber-doradztwo@outlook.com</t>
+          <t>office.marmur-doradztwo@outlook.com</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>https://www.amber-doradztwo-group.eu</t>
+          <t>https://www.marmur-doradztwo-group.eu</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>kontakt.amber-szkolenia@wp.pl</t>
+          <t>kontakt.krokus-szkolenia@wp.pl</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>https://www.amber-szkolenia-group.local</t>
+          <t>https://www.krokus-szkolenia-group.local</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>biuro.amber-media@onet.pl</t>
+          <t>biuro.beskid-media@onet.pl</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://www.amber-media-group.pl</t>
+          <t>https://www.beskid-media-group.pl</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>firma.amber-marketing@o2.pl</t>
+          <t>firma.falcon-marketing@o2.pl</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>https://amber-marketing.eu</t>
+          <t>https://falcon-marketing.eu</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://www.amber-druk-group.local</t>
+          <t>https://www.koral-druk-group.local</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>https://www.amber-informatyka-group.pl</t>
+          <t>https://www.pegaz-informatyka-group.pl</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>office.amber-oprogramowanie@gmail.com</t>
+          <t>office.wektor-oprogramowanie@gmail.com</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>https://www.amber-oprogramowanie-group.com.pl</t>
+          <t>https://www.wektor-oprogramowanie-group.com.pl</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>kontakt.amber-rolnictwo@outlook.com</t>
+          <t>kontakt.kormoran-rolnictwo@outlook.com</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>https://www.amber-rolnictwo.eu</t>
+          <t>https://www.kormoran-rolnictwo.eu</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>biuro.amber-ogrodnictwo@wp.pl</t>
+          <t>biuro.jodelka-ogrodnictwo@wp.pl</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>sekretariat.amber-produkcja@onet.pl</t>
+          <t>sekretariat.marmur-produkcja@onet.pl</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://www.amber-produkcja-group.pl</t>
+          <t>https://www.marmur-produkcja-group.pl</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>firma.amber-przemysl@interia.pl</t>
+          <t>firma.krokus-przemysl@interia.pl</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>https://www.amber-przemysl-group.com.pl</t>
+          <t>https://www.krokus-przemysl-group.com.pl</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://www.amber-ekologia-group.eu</t>
+          <t>https://www.beskid-ekologia-group.eu</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>office.amber-instalacje@yahoo.com</t>
+          <t>office.falcon-instalacje@yahoo.com</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://amber-instalacje.pl</t>
+          <t>https://falcon-instalacje.pl</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>kontakt.amber-nieruchomosci@gmail.com</t>
+          <t>kontakt.koral-nieruchomosci@gmail.com</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>biuro.amber-inwestycje@outlook.com</t>
+          <t>biuro.pegaz-inwestycje@outlook.com</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://www.amber-inwestycje-group.eu</t>
+          <t>https://www.pegaz-inwestycje-group.eu</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>sekretariat.amber-medycyna@wp.pl</t>
+          <t>sekretariat.wektor-medycyna@wp.pl</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>https://www.amber-medycyna-group.local</t>
+          <t>https://www.wektor-medycyna-group.local</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>firma.amber-zdrowie@onet.pl</t>
+          <t>firma.kormoran-zdrowie@onet.pl</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>https://www.amber-zdrowie.pl</t>
+          <t>https://www.kormoran-zdrowie.pl</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>https://amber-urody.com.pl</t>
+          <t>https://jodelka-urody.com.pl</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>https://www.amber-turystyka-group.eu</t>
+          <t>https://www.marmur-turystyka-group.eu</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>office.amber-rozrywka@proton.me</t>
+          <t>office.krokus-rozrywka@proton.me</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>kontakt.amber-gastronomia@yahoo.com</t>
+          <t>kontakt.beskid-gastronomia@yahoo.com</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>https://www.amber-gastronomia-group.pl</t>
+          <t>https://www.beskid-gastronomia-group.pl</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>sekretariat.amber-tekstylia@outlook.com</t>
+          <t>sekretariat.falcon-tekstylia@outlook.com</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>https://amber-tekstylia.eu</t>
+          <t>https://falcon-tekstylia.eu</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t/>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>firma.amber-motoryzacja@wp.pl</t>
+          <t>firma.koral-motoryzacja@wp.pl</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://www.amber-motoryzacja-group.local</t>
+          <t>https://www.koral-motoryzacja-group.local</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t/>
+          <t>62.02.Z</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>https://www.amber-ubezpieczenia-group.pl</t>
+          <t>https://www.pegaz-ubezpieczenia-group.pl</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>office.amber-slusarstwo@o2.pl</t>
+          <t>office.kormoran-slusarstwo@o2.pl</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>https://www.amber-slusarstwo.eu</t>
+          <t>https://www.kormoran-slusarstwo.eu</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t/>
+          <t>1289129807</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7667,12 +7667,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>kontakt.amber-krawiectwo@proton.me</t>
+          <t>kontakt.jodelka-krawiectwo@proton.me</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>https://amber-krawiectwo.local</t>
+          <t>https://jodelka-krawiectwo.local</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>biuro.amber-ochrona@yahoo.com</t>
+          <t>biuro.marmur-ochrona@yahoo.com</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>https://www.amber-ochrona-group.pl</t>
+          <t>https://www.marmur-ochrona-group.pl</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1299288217</t>
+          <t/>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>sekretariat.amber-catering@gmail.com</t>
+          <t>sekretariat.krokus-catering@gmail.com</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>https://www.amber-catering-group.com.pl</t>
+          <t>https://www.krokus-catering-group.com.pl</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>firma.amber-ksiegowosc@outlook.com</t>
+          <t>firma.beskid-ksiegowosc@outlook.com</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>https://www.amber-ksiegowosc-group.eu</t>
+          <t>https://www.beskid-ksiegowosc-group.eu</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>https://bizon-transport.pl</t>
+          <t>https://oaza-transport.pl</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>office.bizon-spedycja@interia.pl</t>
+          <t>office.uran-spedycja@interia.pl</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>https://www.bizon-spedycja-group.com.pl</t>
+          <t>https://www.uran-spedycja-group.com.pl</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>kontakt.bizon-logistyka@o2.pl</t>
+          <t>kontakt.orzel-logistyka@o2.pl</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>https://www.bizon-logistyka-group.eu</t>
+          <t>https://www.orzel-logistyka-group.eu</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>biuro.bizon-handel@proton.me</t>
+          <t>biuro.narew-handel@proton.me</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>https://www.bizon-handel-group.local</t>
+          <t>https://www.narew-handel-group.local</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>sekretariat.bizon-uslugi@yahoo.com</t>
+          <t>sekretariat.granit-uslugi@yahoo.com</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>https://www.bizon-uslugi.pl</t>
+          <t>https://www.granit-uslugi.pl</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>firma.bizon-finanse@gmail.com</t>
+          <t>firma.zorza-finanse@gmail.com</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>https://www.bizon-doradztwo-group.eu</t>
+          <t>https://www.kasprowy-doradztwo-group.eu</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>https://www.bizon-szkolenia-group.local</t>
+          <t>https://www.sudety-szkolenia-group.local</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>office.bizon-media@ubezpiecznia.pl</t>
+          <t>office.echo-media@ubezpiecznia.pl</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>https://www.bizon-media-group.pl</t>
+          <t>https://www.echo-media-group.pl</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>kontakt.bizon-reklama@interia.pl</t>
+          <t>kontakt.jantar-reklama@interia.pl</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>https://www.bizon-reklama.com.pl</t>
+          <t>https://www.jantar-reklama.com.pl</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>biuro.bizon-marketing@o2.pl</t>
+          <t>biuro.oaza-marketing@o2.pl</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>https://bizon-marketing.eu</t>
+          <t>https://oaza-marketing.eu</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>sekretariat.bizon-druk@proton.me</t>
+          <t>sekretariat.uran-druk@proton.me</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>firma.bizon-informatyka@yahoo.com</t>
+          <t>firma.orzel-informatyka@yahoo.com</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>https://www.bizon-informatyka-group.pl</t>
+          <t>https://www.orzel-informatyka-group.pl</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>https://www.bizon-oprogramowanie-group.com.pl</t>
+          <t>https://www.narew-oprogramowanie-group.com.pl</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>https://www.bizon-rolnictwo.eu</t>
+          <t>https://www.granit-rolnictwo.eu</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>office.bizon-ogrodnictwo@wp.pl</t>
+          <t>office.zorza-ogrodnictwo@wp.pl</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>https://bizon-ogrodnictwo.local</t>
+          <t>https://zorza-ogrodnictwo.local</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ÓŁDZKIE</t>
+          <t>ŁÓDZKEI</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>kontakt.bizon-produkcja@onet.pl</t>
+          <t>kontakt.kasprowy-produkcja@onet.pl</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>https://www.bizon-produkcja-group.pl</t>
+          <t>https://www.kasprowy-produkcja-group.pl</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>biuro.bizon-przemysl@interia.pl</t>
+          <t>biuro.sudety-przemysl@interia.pl</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>sekretariat.bizon-ekologia@o2.pl</t>
+          <t>sekretariat.echo-ekologia@o2.pl</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>https://www.bizon-ekologia-group.eu</t>
+          <t>https://www.echo-ekologia-group.eu</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>firma.bizon-energetyka@proton.me</t>
+          <t>firma.jantar-energetyka@proton.me</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>https://www.bizon-energetyka.local</t>
+          <t>https://www.jantar-energetyka.local</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>https://bizon-instalacje.pl</t>
+          <t>https://oaza-instalacje.pl</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>https://www.bizon-nieruchomosci-group.com.pl</t>
+          <t>https://www.uran-nieruchomosci-group.com.pl</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>office.bizon-inwestycje@outlook.com</t>
+          <t>office.orzel-inwestycje@outlook.com</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>https://www.bizon-inwestycje-group.eu</t>
+          <t>https://www.orzel-inwestycje-group.eu</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>kontakt.bizon-medycyna@wp.pl</t>
+          <t>kontakt.narew-medycyna@wp.pl</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>biuro.bizon-zdrowie@onet.pl</t>
+          <t>biuro.granit-zdrowie@onet.pl</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>https://www.bizon-zdrowie.pl</t>
+          <t>https://www.granit-zdrowie.pl</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>sekretariat.bizon-urody@interia.pl</t>
+          <t>sekretariat.zorza-urody@interia.pl</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>https://bizon-urody.com.pl</t>
+          <t>https://zorza-urody.com.pl</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>firma.bizon-turystyka@o2.pl</t>
+          <t>firma.kasprowy-turystyka@o2.pl</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>https://www.bizon-turystyka-group.eu</t>
+          <t>https://www.kasprowy-turystyka-group.eu</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>https://www.bizon-rozrywka-group.local</t>
+          <t>https://www.sudety-rozrywka-group.local</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>https://www.bizon-gastronomia-group.pl</t>
+          <t>https://www.echo-gastronomia-group.pl</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>kontakt.bizon-tekstylia@outlook.com</t>
+          <t>kontakt.oaza-tekstylia@outlook.com</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>https://bizon-tekstylia.eu</t>
+          <t>https://oaza-tekstylia.eu</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>biuro.bizon-motoryzacja@wp.pl</t>
+          <t>biuro.uran-motoryzacja@wp.pl</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>https://www.bizon-motoryzacja-group.local</t>
+          <t>https://www.uran-motoryzacja-group.local</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>sekretariat.bizon-ubezpieczenia@onet.pl</t>
+          <t>sekretariat.orzel-ubezpieczenia@onet.pl</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>https://www.bizon-ubezpieczenia-group.pl</t>
+          <t>https://www.orzel-ubezpieczenia-group.pl</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10973,12 +10973,12 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>firma.bizon-spawalnictwo@interia.pl</t>
+          <t>firma.narew-spawalnictwo@interia.pl</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>https://www.bizon-spawalnictwo-group.com.pl</t>
+          <t>https://www.narew-spawalnictwo-group.com.pl</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>https://www.bizon-slusarstwo.eu</t>
+          <t>https://www.granit-slusarstwo.eu</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>office.bizon-ochrona@yahoo.com</t>
+          <t>office.kasprowy-ochrona@yahoo.com</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>https://www.bizon-ochrona-group.pl</t>
+          <t>https://www.kasprowy-ochrona-group.pl</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>kontakt.bizon-catering@gmail.com</t>
+          <t>kontakt.sudety-catering@gmail.com</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>https://www.bizon-catering-group.com.pl</t>
+          <t>https://www.sudety-catering-group.com.pl</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11408,12 +11408,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>biuro.bizon-ksiegowosc@outlook.com</t>
+          <t>biuro.echo-ksiegowosc@outlook.com</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>https://www.bizon-ksiegowosc-group.eu</t>
+          <t>https://www.echo-ksiegowosc-group.eu</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>sekretariat.canyon-budownictwo@wp.pl</t>
+          <t>sekretariat.tytan-budownictwo@wp.pl</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>https://www.canyon-budownictwo.local</t>
+          <t>https://www.tytan-budownictwo.local</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11582,12 +11582,12 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>firma.canyon-transportonet.pl</t>
+          <t>firma.sokol-transportonet.pl</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>https://canyon-transport.pl</t>
+          <t>https://sokol-transport.pl</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>https://www.canyon-logistyka-group.eu</t>
+          <t>https://www.topaz-logistyka-group.eu</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>office.canyon-handel@proton.me</t>
+          <t>office.olimp-handel@proton.me</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>https://www.canyon-handel-group.local</t>
+          <t>https://www.olimp-handel-group.local</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>kontakt.canyon-uslugi@yahoo.com</t>
+          <t>kontakt.rysy-uslugi@yahoo.com</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>https://www.canyon-uslugi.pl</t>
+          <t>https://www.rysy-uslugi.pl</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12017,12 +12017,12 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>biuro.canyon-finanse@gmail.com</t>
+          <t>biuro.baltyk-finanse@gmail.com</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>https://canyon-finanse.com.pl</t>
+          <t>https://baltyk-finanse.com.pl</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>sekretariat.canyon-doradztwo@outlook.com</t>
+          <t>sekretariat.delfin-doradztwo@outlook.com</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>https://www.canyon-doradztwo-group.eu</t>
+          <t>https://www.delfin-doradztwo-group.eu</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>firma.canyon-szkolenia@wp.pl</t>
+          <t>firma.ikar-szkolenia@wp.pl</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>https://www.canyon-media-group.pl</t>
+          <t>https://www.neon-media-group.pl</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>https://www.canyon-reklama.com.pl</t>
+          <t>https://www.tytan-reklama.com.pl</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>office.canyon-marketing@o2.pl</t>
+          <t>office.sokol-marketing@o2.pl</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>https://canyon-marketing.eu</t>
+          <t>https://sokol-marketing.eu</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>kontakt.canyon-druk@proton.me</t>
+          <t>kontakt.pilica-druk@proton.me</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>https://www.canyon-druk-group.local</t>
+          <t>https://www.pilica-druk-group.local</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>biuro.canyon-informatyka@yahoo.com</t>
+          <t>biuro.topaz-informatyka@yahoo.com</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>https://www.canyon-informatyka-group.pl</t>
+          <t>https://www.topaz-informatyka-group.pl</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>sekretariat.canyon-oprogramowanie@gmail.com</t>
+          <t>sekretariat.olimp-oprogramowanie@gmail.com</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>firma.canyon-rolnictwo@outlook.com</t>
+          <t>firma.rysy-rolnictwo@outlook.com</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>https://www.canyon-rolnictwo.eu</t>
+          <t>https://www.rysy-rolnictwo.eu</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>https://canyon-ogrodnictwo.local</t>
+          <t>https://baltyk-ogrodnictwo.local</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>https://www.canyon-produkcja-group.pl</t>
+          <t>https://www.delfin-produkcja-group.pl</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>office.canyon-przemysl@interia.pl</t>
+          <t>office.ikar-przemysl@interia.pl</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>https://www.canyon-przemysl-group.com.pl</t>
+          <t>https://www.ikar-przemysl-group.com.pl</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>kontakt.canyon-ekologia@abxza.pl</t>
+          <t>kontakt.neon-ekologia@abxza.pl</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>https://www.canyon-ekologia-group.eu</t>
+          <t>https://www.neon-ekologia-group.eu</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>biuro.canyon-energetyka@proton.me</t>
+          <t>biuro.tytan-energetyka@proton.me</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>sekretariat.canyon-instalacje@yahoo.com</t>
+          <t>sekretariat.sokol-instalacje@yahoo.com</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>https://canyon-instalacje.pl</t>
+          <t>https://sokol-instalacje.pl</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>firma.canyon-nieruchomosci@gmail.com</t>
+          <t>firma.pilica-nieruchomosci@gmail.com</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>https://www.canyon-nieruchomosci-group.com.pl</t>
+          <t>https://www.pilica-nieruchomosci-group.com.pl</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>https://www.canyon-inwestycje-group.eu</t>
+          <t>https://www.topaz-inwestycje-group.eu</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>https://www.canyon-medycyna-group.local</t>
+          <t>https://www.olimp-medycyna-group.local</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>office.canyon-zdrowie@onet.pl</t>
+          <t>office.rysy-zdrowie@onet.pl</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>https://www.canyon-zdrowie.pl</t>
+          <t>https://www.rysy-zdrowie.pl</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>kontakt.canyon-urody@interia.pl</t>
+          <t>kontakt.baltyk-urody@interia.pl</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Canyon Tursytyka S. A.</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13844,12 +13844,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>biuro.canyon-turystyka@o2.pl</t>
+          <t>biuro.delfin-turystyka@o2.pl</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>https://www.canyon-turystyka-group.eu</t>
+          <t>https://www.delfin-turystyka-group.eu</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>sekretariat.canyon-rozrywka@proton.me</t>
+          <t>sekretariat.ikar-rozrywka@proton.me</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>https://www.canyon-rozrywka-group.local</t>
+          <t>https://www.ikar-rozrywka-group.local</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>firma.canyon-gastronomia@yahoo.com</t>
+          <t>firma.neon-gastronomia@yahoo.com</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>https://www.canyon-gastronomia-group.pl</t>
+          <t>https://www.neon-gastronomia-group.pl</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>https://canyon-tekstylia.eu</t>
+          <t>https://sokol-tekstylia.eu</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>office.canyon-motoryzacja@wp.pl</t>
+          <t>office.pilica-motoryzacja@wp.pl</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14366,12 +14366,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>kontakt.canyon-ubezpieczenia@onet.pl</t>
+          <t>kontakt.topaz-ubezpieczenia@onet.pl</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>https://www.canyon-ubezpieczenia-group.pl</t>
+          <t>https://www.topaz-ubezpieczenia-group.pl</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14453,12 +14453,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>biuro.canyon-spawalnictwo@interia.pl</t>
+          <t>biuro.olimp-spawalnictwo@interia.pl</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>https://www.canyon-spawalnictwo-group.com.pl</t>
+          <t>https://www.olimp-spawalnictwo-group.com.pl</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14540,12 +14540,12 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>sekretariat.canyon-slusarstwo@o2.pl</t>
+          <t>sekretariat.rysy-slusarstwo@o2.pl</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>https://www.canyon-slusarstwo.eu</t>
+          <t>https://www.rysy-slusarstwo.eu</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14627,12 +14627,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>firma.canyon-krawiectwo@proton.me</t>
+          <t>firma.baltyk-krawiectwo@proton.me</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>https://canyon-krawiectwo.local</t>
+          <t>https://baltyk-krawiectwo.local</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>https://www.canyon-ochrona-group.pl</t>
+          <t>https://www.delfin-ochrona-group.pl</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -14888,12 +14888,12 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>office.canyon-ksiegowosc@outlook.com</t>
+          <t>office.neon-ksiegowosc@outlook.com</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>https://www.canyon-ksiegowosc-group.eu</t>
+          <t>https://www.neon-ksiegowosc-group.eu</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
